--- a/ET/Unity/Assets/Config/Excel/BulletConfig.xlsx
+++ b/ET/Unity/Assets/Config/Excel/BulletConfig.xlsx
@@ -66,7 +66,7 @@
     <t>ID</t>
   </si>
   <si>
-    <t>速度</t>
+    <t>速度/10000</t>
   </si>
   <si>
     <t>伤害</t>
@@ -75,7 +75,7 @@
     <t>飞行类型</t>
   </si>
   <si>
-    <t>飞行参数</t>
+    <t>飞行参数/10000</t>
   </si>
   <si>
     <t>子弹类型</t>
@@ -87,13 +87,13 @@
     <t>锁定追踪</t>
   </si>
   <si>
-    <t>最大飞行距离</t>
+    <t>最大飞行距离/10000</t>
   </si>
   <si>
     <t>寻敌配置ID</t>
   </si>
   <si>
-    <t>碰撞半径</t>
+    <t>碰撞半径/100</t>
   </si>
   <si>
     <t>预制体路径</t>
@@ -172,7 +172,7 @@
     <t>炸弹</t>
   </si>
   <si>
-    <t>50,20</t>
+    <t>500,20</t>
   </si>
   <si>
     <t>Assets/Bundles/Prefabs/Bullet/bullet_zhadan.prefab</t>
@@ -1285,8 +1285,9 @@
     <col min="2" max="2" width="9.23333333333333" customWidth="1"/>
     <col min="3" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="17.3" customWidth="1"/>
-    <col min="9" max="11" width="16" customWidth="1"/>
-    <col min="13" max="13" width="15.25" customWidth="1"/>
+    <col min="9" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="18.75" customWidth="1"/>
+    <col min="13" max="13" width="17.375" customWidth="1"/>
     <col min="14" max="14" width="56" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1412,7 +1413,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="E6" s="1">
         <v>30</v>
@@ -1433,13 +1434,13 @@
         <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>8</v>
+        <v>80000</v>
       </c>
       <c r="L6" s="1">
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>28</v>
@@ -1453,7 +1454,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="7">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="E7" s="7">
         <v>20</v>
@@ -1474,13 +1475,13 @@
         <v>0</v>
       </c>
       <c r="K7" s="8">
-        <v>8</v>
+        <v>80000</v>
       </c>
       <c r="L7" s="8">
         <v>0</v>
       </c>
       <c r="M7" s="8">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N7" s="8" t="s">
         <v>31</v>
